--- a/TestFiles/ExcelFiles/CaseRate.xlsx
+++ b/TestFiles/ExcelFiles/CaseRate.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>10.42</v>
+        <v>12.5</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/CaseRate.xlsx
+++ b/TestFiles/ExcelFiles/CaseRate.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>3.69</v>
+        <v>9.93</v>
       </c>
     </row>
   </sheetData>
